--- a/config/auth.xlsx
+++ b/config/auth.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GN0662\Project\chessapp\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEA38844-21B5-409A-8A47-59A45A806FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068ABCD6-17B2-4B7D-B5B8-9493C36D14B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{F4088B99-184C-4B1A-9868-EBBC981118E7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>username</t>
   </si>
@@ -50,10 +50,28 @@
     <t>C@turc1l1k</t>
   </si>
   <si>
-    <t>caturjun26</t>
-  </si>
-  <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>Caturjun26</t>
+  </si>
+  <si>
+    <t>Izuan87</t>
+  </si>
+  <si>
+    <t>Admin14</t>
+  </si>
+  <si>
+    <t>CatH1jau</t>
+  </si>
+  <si>
+    <t>Champ34</t>
+  </si>
+  <si>
+    <t>CC7</t>
+  </si>
+  <si>
+    <t>testcc</t>
   </si>
 </sst>
 </file>
@@ -436,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A315825B-6EAD-4E08-B2DB-63C6734F7961}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.90625" customWidth="1"/>
@@ -450,18 +468,62 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
